--- a/docs/Sundial_Solar_Fields_by_Section.xlsx
+++ b/docs/Sundial_Solar_Fields_by_Section.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TimMurphy\Projects\harmon-crm\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TimMurphy\Projects\sundial-core\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A75F35C-BF77-4AB7-B1CD-8CDDBF55AE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B20138-22AA-4927-BD85-0D238B72B9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7012,10 +7012,10 @@
         <v>13</v>
       </c>
       <c r="I65" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J65" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">

--- a/docs/Sundial_Solar_Fields_by_Section.xlsx
+++ b/docs/Sundial_Solar_Fields_by_Section.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TimMurphy\Projects\sundial-core\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B20138-22AA-4927-BD85-0D238B72B9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA1B9EC-10AB-4954-81EE-DF27EAC34CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fields by Section" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4737" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4779" uniqueCount="1528">
   <si>
     <t>Section</t>
   </si>
@@ -4559,6 +4559,51 @@
   </si>
   <si>
     <t>hidden</t>
+  </si>
+  <si>
+    <t>NS Adder 1 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_1_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price for NS Adder 1</t>
+  </si>
+  <si>
+    <t>NS Adder 2 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_2_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price for NS Adder 2</t>
+  </si>
+  <si>
+    <t>NS Adder 3 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_3_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price for NS Adder 3</t>
+  </si>
+  <si>
+    <t>NS Adder 4 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_4_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price for NS Adder 4</t>
+  </si>
+  <si>
+    <t>NS Adder 5 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_5_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price for NS Adder 5</t>
   </si>
 </sst>
 </file>
@@ -4935,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J474"/>
+  <dimension ref="A1:J479"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.875" customWidth="1"/>
@@ -16559,22 +16604,16 @@
         <v>930</v>
       </c>
       <c r="B364" t="s">
-        <v>1136</v>
+        <v>1513</v>
       </c>
       <c r="C364" t="s">
-        <v>1137</v>
+        <v>1514</v>
       </c>
       <c r="D364" t="s">
-        <v>1124</v>
+        <v>229</v>
       </c>
       <c r="E364" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F364" t="s">
-        <v>13</v>
-      </c>
-      <c r="G364" t="s">
-        <v>13</v>
+        <v>1515</v>
       </c>
       <c r="H364" t="s">
         <v>848</v>
@@ -16591,16 +16630,16 @@
         <v>930</v>
       </c>
       <c r="B365" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C365" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="D365" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E365" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="F365" t="s">
         <v>13</v>
@@ -16612,10 +16651,10 @@
         <v>848</v>
       </c>
       <c r="I365" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J365" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.25">
@@ -16623,16 +16662,16 @@
         <v>930</v>
       </c>
       <c r="B366" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C366" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="D366" t="s">
-        <v>830</v>
+        <v>1128</v>
       </c>
       <c r="E366" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F366" t="s">
         <v>13</v>
@@ -16655,16 +16694,16 @@
         <v>930</v>
       </c>
       <c r="B367" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C367" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="D367" t="s">
-        <v>918</v>
+        <v>830</v>
       </c>
       <c r="E367" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="F367" t="s">
         <v>13</v>
@@ -16687,16 +16726,16 @@
         <v>930</v>
       </c>
       <c r="B368" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="C368" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D368" t="s">
-        <v>1124</v>
+        <v>918</v>
       </c>
       <c r="E368" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="F368" t="s">
         <v>13</v>
@@ -16708,10 +16747,10 @@
         <v>848</v>
       </c>
       <c r="I368" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="J368" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.25">
@@ -16719,31 +16758,25 @@
         <v>930</v>
       </c>
       <c r="B369" t="s">
-        <v>1146</v>
+        <v>1516</v>
       </c>
       <c r="C369" t="s">
-        <v>1147</v>
+        <v>1517</v>
       </c>
       <c r="D369" t="s">
-        <v>1128</v>
+        <v>229</v>
       </c>
       <c r="E369" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F369" t="s">
-        <v>13</v>
-      </c>
-      <c r="G369" t="s">
-        <v>13</v>
+        <v>1518</v>
       </c>
       <c r="H369" t="s">
         <v>848</v>
       </c>
       <c r="I369" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J369" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.25">
@@ -16751,16 +16784,16 @@
         <v>930</v>
       </c>
       <c r="B370" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="C370" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="D370" t="s">
-        <v>830</v>
+        <v>1124</v>
       </c>
       <c r="E370" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="F370" t="s">
         <v>13</v>
@@ -16772,10 +16805,10 @@
         <v>848</v>
       </c>
       <c r="I370" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J370" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.25">
@@ -16783,16 +16816,16 @@
         <v>930</v>
       </c>
       <c r="B371" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="C371" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="D371" t="s">
-        <v>918</v>
+        <v>1128</v>
       </c>
       <c r="E371" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="F371" t="s">
         <v>13</v>
@@ -16815,16 +16848,16 @@
         <v>930</v>
       </c>
       <c r="B372" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="C372" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="D372" t="s">
-        <v>1124</v>
+        <v>830</v>
       </c>
       <c r="E372" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="F372" t="s">
         <v>13</v>
@@ -16836,10 +16869,10 @@
         <v>848</v>
       </c>
       <c r="I372" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="J372" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.25">
@@ -16847,16 +16880,16 @@
         <v>930</v>
       </c>
       <c r="B373" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="C373" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="D373" t="s">
-        <v>1156</v>
+        <v>918</v>
       </c>
       <c r="E373" t="s">
-        <v>1157</v>
+        <v>1135</v>
       </c>
       <c r="F373" t="s">
         <v>13</v>
@@ -16879,31 +16912,25 @@
         <v>930</v>
       </c>
       <c r="B374" t="s">
-        <v>1158</v>
+        <v>1519</v>
       </c>
       <c r="C374" t="s">
-        <v>1159</v>
+        <v>1520</v>
       </c>
       <c r="D374" t="s">
-        <v>830</v>
+        <v>229</v>
       </c>
       <c r="E374" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F374" t="s">
-        <v>13</v>
-      </c>
-      <c r="G374" t="s">
-        <v>13</v>
+        <v>1521</v>
       </c>
       <c r="H374" t="s">
         <v>848</v>
       </c>
       <c r="I374" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J374" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.25">
@@ -16911,16 +16938,16 @@
         <v>930</v>
       </c>
       <c r="B375" t="s">
-        <v>1161</v>
+        <v>1152</v>
       </c>
       <c r="C375" t="s">
-        <v>1162</v>
+        <v>1153</v>
       </c>
       <c r="D375" t="s">
-        <v>1163</v>
+        <v>1124</v>
       </c>
       <c r="E375" t="s">
-        <v>1164</v>
+        <v>1125</v>
       </c>
       <c r="F375" t="s">
         <v>13</v>
@@ -16932,10 +16959,10 @@
         <v>848</v>
       </c>
       <c r="I375" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J375" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.25">
@@ -16943,16 +16970,16 @@
         <v>930</v>
       </c>
       <c r="B376" t="s">
-        <v>1165</v>
+        <v>1154</v>
       </c>
       <c r="C376" t="s">
-        <v>1166</v>
+        <v>1155</v>
       </c>
       <c r="D376" t="s">
-        <v>1124</v>
+        <v>1156</v>
       </c>
       <c r="E376" t="s">
-        <v>1125</v>
+        <v>1157</v>
       </c>
       <c r="F376" t="s">
         <v>13</v>
@@ -16964,10 +16991,10 @@
         <v>848</v>
       </c>
       <c r="I376" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="J376" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.25">
@@ -16975,16 +17002,16 @@
         <v>930</v>
       </c>
       <c r="B377" t="s">
-        <v>1167</v>
+        <v>1158</v>
       </c>
       <c r="C377" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="D377" t="s">
-        <v>1156</v>
+        <v>830</v>
       </c>
       <c r="E377" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="F377" t="s">
         <v>13</v>
@@ -17007,16 +17034,16 @@
         <v>930</v>
       </c>
       <c r="B378" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="C378" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="D378" t="s">
-        <v>830</v>
+        <v>1163</v>
       </c>
       <c r="E378" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="F378" t="s">
         <v>13</v>
@@ -17039,89 +17066,83 @@
         <v>930</v>
       </c>
       <c r="B379" t="s">
-        <v>1171</v>
+        <v>1522</v>
       </c>
       <c r="C379" t="s">
-        <v>1172</v>
+        <v>1523</v>
       </c>
       <c r="D379" t="s">
-        <v>1163</v>
+        <v>229</v>
       </c>
       <c r="E379" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F379" t="s">
-        <v>13</v>
-      </c>
-      <c r="G379" t="s">
-        <v>13</v>
+        <v>1524</v>
       </c>
       <c r="H379" t="s">
         <v>848</v>
       </c>
       <c r="I379" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J379" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>1173</v>
+        <v>930</v>
       </c>
       <c r="B380" t="s">
-        <v>1174</v>
+        <v>1165</v>
       </c>
       <c r="C380" t="s">
-        <v>1175</v>
+        <v>1166</v>
       </c>
       <c r="D380" t="s">
-        <v>1176</v>
+        <v>1124</v>
       </c>
       <c r="E380" t="s">
-        <v>1177</v>
+        <v>1125</v>
       </c>
       <c r="F380" t="s">
         <v>13</v>
       </c>
       <c r="G380" t="s">
-        <v>1178</v>
+        <v>13</v>
       </c>
       <c r="H380" t="s">
-        <v>13</v>
+        <v>848</v>
       </c>
       <c r="I380" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J380" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>1173</v>
+        <v>930</v>
       </c>
       <c r="B381" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="C381" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="D381" t="s">
-        <v>1176</v>
+        <v>1156</v>
       </c>
       <c r="E381" t="s">
-        <v>1181</v>
+        <v>1157</v>
       </c>
       <c r="F381" t="s">
         <v>13</v>
       </c>
       <c r="G381" t="s">
-        <v>1182</v>
+        <v>13</v>
       </c>
       <c r="H381" t="s">
-        <v>13</v>
+        <v>848</v>
       </c>
       <c r="I381" t="s">
         <v>1512</v>
@@ -17132,28 +17153,28 @@
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>1173</v>
+        <v>930</v>
       </c>
       <c r="B382" t="s">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="C382" t="s">
-        <v>1184</v>
+        <v>1170</v>
       </c>
       <c r="D382" t="s">
         <v>830</v>
       </c>
       <c r="E382" t="s">
-        <v>1185</v>
+        <v>1160</v>
       </c>
       <c r="F382" t="s">
         <v>13</v>
       </c>
       <c r="G382" t="s">
-        <v>1186</v>
+        <v>13</v>
       </c>
       <c r="H382" t="s">
-        <v>13</v>
+        <v>848</v>
       </c>
       <c r="I382" t="s">
         <v>1512</v>
@@ -17164,28 +17185,28 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>1173</v>
+        <v>930</v>
       </c>
       <c r="B383" t="s">
-        <v>1187</v>
+        <v>1171</v>
       </c>
       <c r="C383" t="s">
-        <v>1188</v>
+        <v>1172</v>
       </c>
       <c r="D383" t="s">
-        <v>895</v>
+        <v>1163</v>
       </c>
       <c r="E383" t="s">
-        <v>1189</v>
+        <v>1164</v>
       </c>
       <c r="F383" t="s">
         <v>13</v>
       </c>
       <c r="G383" t="s">
-        <v>1190</v>
+        <v>13</v>
       </c>
       <c r="H383" t="s">
-        <v>13</v>
+        <v>848</v>
       </c>
       <c r="I383" t="s">
         <v>1512</v>
@@ -17196,31 +17217,25 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>1173</v>
+        <v>930</v>
       </c>
       <c r="B384" t="s">
-        <v>1191</v>
+        <v>1525</v>
       </c>
       <c r="C384" t="s">
-        <v>1192</v>
+        <v>1526</v>
       </c>
       <c r="D384" t="s">
-        <v>1193</v>
+        <v>229</v>
       </c>
       <c r="E384" t="s">
-        <v>1194</v>
-      </c>
-      <c r="F384" t="s">
-        <v>13</v>
-      </c>
-      <c r="G384" t="s">
-        <v>1195</v>
+        <v>1527</v>
       </c>
       <c r="H384" t="s">
-        <v>13</v>
+        <v>848</v>
       </c>
       <c r="I384" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J384" t="s">
         <v>1511</v>
@@ -17231,31 +17246,31 @@
         <v>1173</v>
       </c>
       <c r="B385" t="s">
-        <v>1196</v>
+        <v>1174</v>
       </c>
       <c r="C385" t="s">
-        <v>1197</v>
+        <v>1175</v>
       </c>
       <c r="D385" t="s">
-        <v>1193</v>
+        <v>1176</v>
       </c>
       <c r="E385" t="s">
-        <v>1198</v>
+        <v>1177</v>
       </c>
       <c r="F385" t="s">
         <v>13</v>
       </c>
       <c r="G385" t="s">
-        <v>1199</v>
+        <v>1178</v>
       </c>
       <c r="H385" t="s">
         <v>13</v>
       </c>
       <c r="I385" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="J385" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.25">
@@ -17263,22 +17278,22 @@
         <v>1173</v>
       </c>
       <c r="B386" t="s">
-        <v>1200</v>
+        <v>1179</v>
       </c>
       <c r="C386" t="s">
-        <v>1201</v>
+        <v>1180</v>
       </c>
       <c r="D386" t="s">
-        <v>1193</v>
+        <v>1176</v>
       </c>
       <c r="E386" t="s">
-        <v>1202</v>
+        <v>1181</v>
       </c>
       <c r="F386" t="s">
         <v>13</v>
       </c>
       <c r="G386" t="s">
-        <v>1203</v>
+        <v>1182</v>
       </c>
       <c r="H386" t="s">
         <v>13</v>
@@ -17287,7 +17302,7 @@
         <v>1512</v>
       </c>
       <c r="J386" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.25">
@@ -17295,22 +17310,22 @@
         <v>1173</v>
       </c>
       <c r="B387" t="s">
-        <v>1204</v>
+        <v>1183</v>
       </c>
       <c r="C387" t="s">
-        <v>1205</v>
+        <v>1184</v>
       </c>
       <c r="D387" t="s">
-        <v>1193</v>
+        <v>830</v>
       </c>
       <c r="E387" t="s">
-        <v>1206</v>
+        <v>1185</v>
       </c>
       <c r="F387" t="s">
         <v>13</v>
       </c>
       <c r="G387" t="s">
-        <v>1207</v>
+        <v>1186</v>
       </c>
       <c r="H387" t="s">
         <v>13</v>
@@ -17319,7 +17334,7 @@
         <v>1512</v>
       </c>
       <c r="J387" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.25">
@@ -17327,22 +17342,22 @@
         <v>1173</v>
       </c>
       <c r="B388" t="s">
-        <v>1208</v>
+        <v>1187</v>
       </c>
       <c r="C388" t="s">
-        <v>1209</v>
+        <v>1188</v>
       </c>
       <c r="D388" t="s">
-        <v>830</v>
+        <v>895</v>
       </c>
       <c r="E388" t="s">
-        <v>1210</v>
+        <v>1189</v>
       </c>
       <c r="F388" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G388" t="s">
-        <v>1211</v>
+        <v>1190</v>
       </c>
       <c r="H388" t="s">
         <v>13</v>
@@ -17359,22 +17374,22 @@
         <v>1173</v>
       </c>
       <c r="B389" t="s">
-        <v>1212</v>
+        <v>1191</v>
       </c>
       <c r="C389" t="s">
-        <v>1213</v>
+        <v>1192</v>
       </c>
       <c r="D389" t="s">
-        <v>830</v>
+        <v>1193</v>
       </c>
       <c r="E389" t="s">
-        <v>1214</v>
+        <v>1194</v>
       </c>
       <c r="F389" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G389" t="s">
-        <v>1215</v>
+        <v>1195</v>
       </c>
       <c r="H389" t="s">
         <v>13</v>
@@ -17383,7 +17398,7 @@
         <v>1512</v>
       </c>
       <c r="J389" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.25">
@@ -17391,31 +17406,31 @@
         <v>1173</v>
       </c>
       <c r="B390" t="s">
-        <v>1216</v>
+        <v>1196</v>
       </c>
       <c r="C390" t="s">
-        <v>1217</v>
+        <v>1197</v>
       </c>
       <c r="D390" t="s">
-        <v>830</v>
+        <v>1193</v>
       </c>
       <c r="E390" t="s">
-        <v>1218</v>
+        <v>1198</v>
       </c>
       <c r="F390" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G390" t="s">
-        <v>1219</v>
+        <v>1199</v>
       </c>
       <c r="H390" t="s">
         <v>13</v>
       </c>
       <c r="I390" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="J390" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.25">
@@ -17423,22 +17438,22 @@
         <v>1173</v>
       </c>
       <c r="B391" t="s">
-        <v>1220</v>
+        <v>1200</v>
       </c>
       <c r="C391" t="s">
-        <v>1221</v>
+        <v>1201</v>
       </c>
       <c r="D391" t="s">
-        <v>830</v>
+        <v>1193</v>
       </c>
       <c r="E391" t="s">
-        <v>1222</v>
+        <v>1202</v>
       </c>
       <c r="F391" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G391" t="s">
-        <v>1219</v>
+        <v>1203</v>
       </c>
       <c r="H391" t="s">
         <v>13</v>
@@ -17447,7 +17462,7 @@
         <v>1512</v>
       </c>
       <c r="J391" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.25">
@@ -17455,22 +17470,22 @@
         <v>1173</v>
       </c>
       <c r="B392" t="s">
-        <v>1223</v>
+        <v>1204</v>
       </c>
       <c r="C392" t="s">
-        <v>1224</v>
+        <v>1205</v>
       </c>
       <c r="D392" t="s">
-        <v>830</v>
+        <v>1193</v>
       </c>
       <c r="E392" t="s">
-        <v>1225</v>
+        <v>1206</v>
       </c>
       <c r="F392" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G392" t="s">
-        <v>1226</v>
+        <v>1207</v>
       </c>
       <c r="H392" t="s">
         <v>13</v>
@@ -17479,7 +17494,7 @@
         <v>1512</v>
       </c>
       <c r="J392" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.25">
@@ -17487,22 +17502,22 @@
         <v>1173</v>
       </c>
       <c r="B393" t="s">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="C393" t="s">
-        <v>1228</v>
+        <v>1209</v>
       </c>
       <c r="D393" t="s">
         <v>830</v>
       </c>
       <c r="E393" t="s">
-        <v>1229</v>
+        <v>1210</v>
       </c>
       <c r="F393" t="s">
         <v>406</v>
       </c>
       <c r="G393" t="s">
-        <v>1230</v>
+        <v>1211</v>
       </c>
       <c r="H393" t="s">
         <v>13</v>
@@ -17519,22 +17534,22 @@
         <v>1173</v>
       </c>
       <c r="B394" t="s">
-        <v>1231</v>
+        <v>1212</v>
       </c>
       <c r="C394" t="s">
-        <v>1232</v>
+        <v>1213</v>
       </c>
       <c r="D394" t="s">
         <v>830</v>
       </c>
       <c r="E394" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="F394" t="s">
         <v>406</v>
       </c>
       <c r="G394" t="s">
-        <v>13</v>
+        <v>1215</v>
       </c>
       <c r="H394" t="s">
         <v>13</v>
@@ -17551,22 +17566,22 @@
         <v>1173</v>
       </c>
       <c r="B395" t="s">
-        <v>1234</v>
+        <v>1216</v>
       </c>
       <c r="C395" t="s">
-        <v>1235</v>
+        <v>1217</v>
       </c>
       <c r="D395" t="s">
         <v>830</v>
       </c>
       <c r="E395" t="s">
-        <v>1236</v>
+        <v>1218</v>
       </c>
       <c r="F395" t="s">
         <v>406</v>
       </c>
       <c r="G395" t="s">
-        <v>1237</v>
+        <v>1219</v>
       </c>
       <c r="H395" t="s">
         <v>13</v>
@@ -17583,22 +17598,22 @@
         <v>1173</v>
       </c>
       <c r="B396" t="s">
-        <v>1238</v>
+        <v>1220</v>
       </c>
       <c r="C396" t="s">
-        <v>1239</v>
+        <v>1221</v>
       </c>
       <c r="D396" t="s">
         <v>830</v>
       </c>
       <c r="E396" t="s">
-        <v>1240</v>
+        <v>1222</v>
       </c>
       <c r="F396" t="s">
         <v>406</v>
       </c>
       <c r="G396" t="s">
-        <v>13</v>
+        <v>1219</v>
       </c>
       <c r="H396" t="s">
         <v>13</v>
@@ -17615,22 +17630,22 @@
         <v>1173</v>
       </c>
       <c r="B397" t="s">
-        <v>1241</v>
+        <v>1223</v>
       </c>
       <c r="C397" t="s">
-        <v>1242</v>
+        <v>1224</v>
       </c>
       <c r="D397" t="s">
-        <v>1243</v>
+        <v>830</v>
       </c>
       <c r="E397" t="s">
-        <v>1244</v>
+        <v>1225</v>
       </c>
       <c r="F397" t="s">
         <v>406</v>
       </c>
       <c r="G397" t="s">
-        <v>13</v>
+        <v>1226</v>
       </c>
       <c r="H397" t="s">
         <v>13</v>
@@ -17647,22 +17662,22 @@
         <v>1173</v>
       </c>
       <c r="B398" t="s">
-        <v>1245</v>
+        <v>1227</v>
       </c>
       <c r="C398" t="s">
-        <v>1246</v>
+        <v>1228</v>
       </c>
       <c r="D398" t="s">
-        <v>1247</v>
+        <v>830</v>
       </c>
       <c r="E398" t="s">
-        <v>1248</v>
+        <v>1229</v>
       </c>
       <c r="F398" t="s">
         <v>406</v>
       </c>
       <c r="G398" t="s">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="H398" t="s">
         <v>13</v>
@@ -17676,22 +17691,22 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1250</v>
+        <v>1173</v>
       </c>
       <c r="B399" t="s">
-        <v>1251</v>
+        <v>1231</v>
       </c>
       <c r="C399" t="s">
-        <v>1252</v>
+        <v>1232</v>
       </c>
       <c r="D399" t="s">
-        <v>1253</v>
+        <v>830</v>
       </c>
       <c r="E399" t="s">
-        <v>1254</v>
+        <v>1233</v>
       </c>
       <c r="F399" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G399" t="s">
         <v>13</v>
@@ -17708,25 +17723,25 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1250</v>
+        <v>1173</v>
       </c>
       <c r="B400" t="s">
-        <v>1255</v>
+        <v>1234</v>
       </c>
       <c r="C400" t="s">
-        <v>1256</v>
+        <v>1235</v>
       </c>
       <c r="D400" t="s">
-        <v>918</v>
+        <v>830</v>
       </c>
       <c r="E400" t="s">
-        <v>1257</v>
+        <v>1236</v>
       </c>
       <c r="F400" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G400" t="s">
-        <v>13</v>
+        <v>1237</v>
       </c>
       <c r="H400" t="s">
         <v>13</v>
@@ -17740,22 +17755,22 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1250</v>
+        <v>1173</v>
       </c>
       <c r="B401" t="s">
-        <v>1258</v>
+        <v>1238</v>
       </c>
       <c r="C401" t="s">
-        <v>1259</v>
+        <v>1239</v>
       </c>
       <c r="D401" t="s">
         <v>830</v>
       </c>
       <c r="E401" t="s">
-        <v>1260</v>
+        <v>1240</v>
       </c>
       <c r="F401" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G401" t="s">
         <v>13</v>
@@ -17772,22 +17787,22 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1250</v>
+        <v>1173</v>
       </c>
       <c r="B402" t="s">
-        <v>1261</v>
+        <v>1241</v>
       </c>
       <c r="C402" t="s">
-        <v>1262</v>
+        <v>1242</v>
       </c>
       <c r="D402" t="s">
-        <v>830</v>
+        <v>1243</v>
       </c>
       <c r="E402" t="s">
-        <v>1263</v>
+        <v>1244</v>
       </c>
       <c r="F402" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G402" t="s">
         <v>13</v>
@@ -17804,25 +17819,25 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1250</v>
+        <v>1173</v>
       </c>
       <c r="B403" t="s">
-        <v>1264</v>
+        <v>1245</v>
       </c>
       <c r="C403" t="s">
-        <v>1265</v>
+        <v>1246</v>
       </c>
       <c r="D403" t="s">
-        <v>830</v>
+        <v>1247</v>
       </c>
       <c r="E403" t="s">
-        <v>1266</v>
+        <v>1248</v>
       </c>
       <c r="F403" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G403" t="s">
-        <v>13</v>
+        <v>1249</v>
       </c>
       <c r="H403" t="s">
         <v>13</v>
@@ -17839,16 +17854,16 @@
         <v>1250</v>
       </c>
       <c r="B404" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
       <c r="C404" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
       <c r="D404" t="s">
-        <v>830</v>
+        <v>1253</v>
       </c>
       <c r="E404" t="s">
-        <v>1269</v>
+        <v>1254</v>
       </c>
       <c r="F404" t="s">
         <v>13</v>
@@ -17871,16 +17886,16 @@
         <v>1250</v>
       </c>
       <c r="B405" t="s">
-        <v>1270</v>
+        <v>1255</v>
       </c>
       <c r="C405" t="s">
-        <v>1271</v>
+        <v>1256</v>
       </c>
       <c r="D405" t="s">
-        <v>830</v>
+        <v>918</v>
       </c>
       <c r="E405" t="s">
-        <v>1272</v>
+        <v>1257</v>
       </c>
       <c r="F405" t="s">
         <v>13</v>
@@ -17903,16 +17918,16 @@
         <v>1250</v>
       </c>
       <c r="B406" t="s">
-        <v>1273</v>
+        <v>1258</v>
       </c>
       <c r="C406" t="s">
-        <v>1274</v>
+        <v>1259</v>
       </c>
       <c r="D406" t="s">
         <v>830</v>
       </c>
       <c r="E406" t="s">
-        <v>1275</v>
+        <v>1260</v>
       </c>
       <c r="F406" t="s">
         <v>13</v>
@@ -17935,16 +17950,16 @@
         <v>1250</v>
       </c>
       <c r="B407" t="s">
-        <v>1276</v>
+        <v>1261</v>
       </c>
       <c r="C407" t="s">
-        <v>1277</v>
+        <v>1262</v>
       </c>
       <c r="D407" t="s">
         <v>830</v>
       </c>
       <c r="E407" t="s">
-        <v>1278</v>
+        <v>1263</v>
       </c>
       <c r="F407" t="s">
         <v>13</v>
@@ -17967,16 +17982,16 @@
         <v>1250</v>
       </c>
       <c r="B408" t="s">
-        <v>1279</v>
+        <v>1264</v>
       </c>
       <c r="C408" t="s">
-        <v>1280</v>
+        <v>1265</v>
       </c>
       <c r="D408" t="s">
         <v>830</v>
       </c>
       <c r="E408" t="s">
-        <v>1281</v>
+        <v>1266</v>
       </c>
       <c r="F408" t="s">
         <v>13</v>
@@ -17999,22 +18014,22 @@
         <v>1250</v>
       </c>
       <c r="B409" t="s">
-        <v>1282</v>
+        <v>1267</v>
       </c>
       <c r="C409" t="s">
-        <v>1283</v>
+        <v>1268</v>
       </c>
       <c r="D409" t="s">
         <v>830</v>
       </c>
       <c r="E409" t="s">
-        <v>1284</v>
+        <v>1269</v>
       </c>
       <c r="F409" t="s">
         <v>13</v>
       </c>
       <c r="G409" t="s">
-        <v>1285</v>
+        <v>13</v>
       </c>
       <c r="H409" t="s">
         <v>13</v>
@@ -18031,22 +18046,22 @@
         <v>1250</v>
       </c>
       <c r="B410" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
       <c r="C410" t="s">
-        <v>1287</v>
+        <v>1271</v>
       </c>
       <c r="D410" t="s">
         <v>830</v>
       </c>
       <c r="E410" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
       <c r="F410" t="s">
         <v>13</v>
       </c>
       <c r="G410" t="s">
-        <v>1289</v>
+        <v>13</v>
       </c>
       <c r="H410" t="s">
         <v>13</v>
@@ -18063,16 +18078,16 @@
         <v>1250</v>
       </c>
       <c r="B411" t="s">
-        <v>1290</v>
+        <v>1273</v>
       </c>
       <c r="C411" t="s">
-        <v>1291</v>
+        <v>1274</v>
       </c>
       <c r="D411" t="s">
         <v>830</v>
       </c>
       <c r="E411" t="s">
-        <v>1292</v>
+        <v>1275</v>
       </c>
       <c r="F411" t="s">
         <v>13</v>
@@ -18095,16 +18110,16 @@
         <v>1250</v>
       </c>
       <c r="B412" t="s">
-        <v>1293</v>
+        <v>1276</v>
       </c>
       <c r="C412" t="s">
-        <v>1294</v>
+        <v>1277</v>
       </c>
       <c r="D412" t="s">
         <v>830</v>
       </c>
       <c r="E412" t="s">
-        <v>1295</v>
+        <v>1278</v>
       </c>
       <c r="F412" t="s">
         <v>13</v>
@@ -18127,16 +18142,16 @@
         <v>1250</v>
       </c>
       <c r="B413" t="s">
-        <v>1296</v>
+        <v>1279</v>
       </c>
       <c r="C413" t="s">
-        <v>1297</v>
+        <v>1280</v>
       </c>
       <c r="D413" t="s">
         <v>830</v>
       </c>
       <c r="E413" t="s">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="F413" t="s">
         <v>13</v>
@@ -18159,22 +18174,22 @@
         <v>1250</v>
       </c>
       <c r="B414" t="s">
-        <v>1299</v>
+        <v>1282</v>
       </c>
       <c r="C414" t="s">
-        <v>1300</v>
+        <v>1283</v>
       </c>
       <c r="D414" t="s">
         <v>830</v>
       </c>
       <c r="E414" t="s">
-        <v>1301</v>
+        <v>1284</v>
       </c>
       <c r="F414" t="s">
         <v>13</v>
       </c>
       <c r="G414" t="s">
-        <v>13</v>
+        <v>1285</v>
       </c>
       <c r="H414" t="s">
         <v>13</v>
@@ -18191,22 +18206,22 @@
         <v>1250</v>
       </c>
       <c r="B415" t="s">
-        <v>1302</v>
+        <v>1286</v>
       </c>
       <c r="C415" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
       <c r="D415" t="s">
         <v>830</v>
       </c>
       <c r="E415" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
       <c r="F415" t="s">
         <v>13</v>
       </c>
       <c r="G415" t="s">
-        <v>13</v>
+        <v>1289</v>
       </c>
       <c r="H415" t="s">
         <v>13</v>
@@ -18223,16 +18238,16 @@
         <v>1250</v>
       </c>
       <c r="B416" t="s">
-        <v>1305</v>
+        <v>1290</v>
       </c>
       <c r="C416" t="s">
-        <v>1306</v>
+        <v>1291</v>
       </c>
       <c r="D416" t="s">
         <v>830</v>
       </c>
       <c r="E416" t="s">
-        <v>1307</v>
+        <v>1292</v>
       </c>
       <c r="F416" t="s">
         <v>13</v>
@@ -18255,16 +18270,16 @@
         <v>1250</v>
       </c>
       <c r="B417" t="s">
-        <v>1308</v>
+        <v>1293</v>
       </c>
       <c r="C417" t="s">
-        <v>1309</v>
+        <v>1294</v>
       </c>
       <c r="D417" t="s">
         <v>830</v>
       </c>
       <c r="E417" t="s">
-        <v>1310</v>
+        <v>1295</v>
       </c>
       <c r="F417" t="s">
         <v>13</v>
@@ -18287,16 +18302,16 @@
         <v>1250</v>
       </c>
       <c r="B418" t="s">
-        <v>1311</v>
+        <v>1296</v>
       </c>
       <c r="C418" t="s">
-        <v>1312</v>
+        <v>1297</v>
       </c>
       <c r="D418" t="s">
         <v>830</v>
       </c>
       <c r="E418" t="s">
-        <v>1313</v>
+        <v>1298</v>
       </c>
       <c r="F418" t="s">
         <v>13</v>
@@ -18319,16 +18334,16 @@
         <v>1250</v>
       </c>
       <c r="B419" t="s">
-        <v>1314</v>
+        <v>1299</v>
       </c>
       <c r="C419" t="s">
-        <v>1315</v>
+        <v>1300</v>
       </c>
       <c r="D419" t="s">
-        <v>1316</v>
+        <v>830</v>
       </c>
       <c r="E419" t="s">
-        <v>1317</v>
+        <v>1301</v>
       </c>
       <c r="F419" t="s">
         <v>13</v>
@@ -18351,16 +18366,16 @@
         <v>1250</v>
       </c>
       <c r="B420" t="s">
-        <v>1318</v>
+        <v>1302</v>
       </c>
       <c r="C420" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="D420" t="s">
         <v>830</v>
       </c>
       <c r="E420" t="s">
-        <v>1320</v>
+        <v>1304</v>
       </c>
       <c r="F420" t="s">
         <v>13</v>
@@ -18383,16 +18398,16 @@
         <v>1250</v>
       </c>
       <c r="B421" t="s">
-        <v>1321</v>
+        <v>1305</v>
       </c>
       <c r="C421" t="s">
-        <v>1322</v>
+        <v>1306</v>
       </c>
       <c r="D421" t="s">
         <v>830</v>
       </c>
       <c r="E421" t="s">
-        <v>1323</v>
+        <v>1307</v>
       </c>
       <c r="F421" t="s">
         <v>13</v>
@@ -18415,16 +18430,16 @@
         <v>1250</v>
       </c>
       <c r="B422" t="s">
-        <v>1324</v>
+        <v>1308</v>
       </c>
       <c r="C422" t="s">
-        <v>1325</v>
+        <v>1309</v>
       </c>
       <c r="D422" t="s">
         <v>830</v>
       </c>
       <c r="E422" t="s">
-        <v>1326</v>
+        <v>1310</v>
       </c>
       <c r="F422" t="s">
         <v>13</v>
@@ -18447,16 +18462,16 @@
         <v>1250</v>
       </c>
       <c r="B423" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="C423" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
       <c r="D423" t="s">
         <v>830</v>
       </c>
       <c r="E423" t="s">
-        <v>1326</v>
+        <v>1313</v>
       </c>
       <c r="F423" t="s">
         <v>13</v>
@@ -18479,16 +18494,16 @@
         <v>1250</v>
       </c>
       <c r="B424" t="s">
-        <v>1329</v>
+        <v>1314</v>
       </c>
       <c r="C424" t="s">
-        <v>1330</v>
+        <v>1315</v>
       </c>
       <c r="D424" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E424" t="s">
-        <v>1331</v>
+        <v>1317</v>
       </c>
       <c r="F424" t="s">
         <v>13</v>
@@ -18511,16 +18526,16 @@
         <v>1250</v>
       </c>
       <c r="B425" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="C425" t="s">
-        <v>1333</v>
+        <v>1319</v>
       </c>
       <c r="D425" t="s">
         <v>830</v>
       </c>
       <c r="E425" t="s">
-        <v>1334</v>
+        <v>1320</v>
       </c>
       <c r="F425" t="s">
         <v>13</v>
@@ -18543,16 +18558,16 @@
         <v>1250</v>
       </c>
       <c r="B426" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="C426" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
       <c r="D426" t="s">
         <v>830</v>
       </c>
       <c r="E426" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="F426" t="s">
         <v>13</v>
@@ -18575,16 +18590,16 @@
         <v>1250</v>
       </c>
       <c r="B427" t="s">
-        <v>1338</v>
+        <v>1324</v>
       </c>
       <c r="C427" t="s">
-        <v>1339</v>
+        <v>1325</v>
       </c>
       <c r="D427" t="s">
-        <v>1316</v>
+        <v>830</v>
       </c>
       <c r="E427" t="s">
-        <v>1340</v>
+        <v>1326</v>
       </c>
       <c r="F427" t="s">
         <v>13</v>
@@ -18607,22 +18622,22 @@
         <v>1250</v>
       </c>
       <c r="B428" t="s">
-        <v>1341</v>
+        <v>1327</v>
       </c>
       <c r="C428" t="s">
-        <v>1342</v>
+        <v>1328</v>
       </c>
       <c r="D428" t="s">
         <v>830</v>
       </c>
       <c r="E428" t="s">
-        <v>1343</v>
+        <v>1326</v>
       </c>
       <c r="F428" t="s">
         <v>13</v>
       </c>
       <c r="G428" t="s">
-        <v>1344</v>
+        <v>13</v>
       </c>
       <c r="H428" t="s">
         <v>13</v>
@@ -18639,16 +18654,16 @@
         <v>1250</v>
       </c>
       <c r="B429" t="s">
-        <v>1345</v>
+        <v>1329</v>
       </c>
       <c r="C429" t="s">
-        <v>1346</v>
+        <v>1330</v>
       </c>
       <c r="D429" t="s">
         <v>830</v>
       </c>
       <c r="E429" t="s">
-        <v>1347</v>
+        <v>1331</v>
       </c>
       <c r="F429" t="s">
         <v>13</v>
@@ -18671,22 +18686,22 @@
         <v>1250</v>
       </c>
       <c r="B430" t="s">
-        <v>1348</v>
+        <v>1332</v>
       </c>
       <c r="C430" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="D430" t="s">
         <v>830</v>
       </c>
       <c r="E430" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="F430" t="s">
         <v>13</v>
       </c>
       <c r="G430" t="s">
-        <v>1351</v>
+        <v>13</v>
       </c>
       <c r="H430" t="s">
         <v>13</v>
@@ -18703,22 +18718,22 @@
         <v>1250</v>
       </c>
       <c r="B431" t="s">
-        <v>1352</v>
+        <v>1335</v>
       </c>
       <c r="C431" t="s">
-        <v>1353</v>
+        <v>1336</v>
       </c>
       <c r="D431" t="s">
         <v>830</v>
       </c>
       <c r="E431" t="s">
-        <v>1354</v>
+        <v>1337</v>
       </c>
       <c r="F431" t="s">
         <v>13</v>
       </c>
       <c r="G431" t="s">
-        <v>1355</v>
+        <v>13</v>
       </c>
       <c r="H431" t="s">
         <v>13</v>
@@ -18735,22 +18750,22 @@
         <v>1250</v>
       </c>
       <c r="B432" t="s">
-        <v>1356</v>
+        <v>1338</v>
       </c>
       <c r="C432" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="D432" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E432" t="s">
-        <v>1358</v>
+        <v>1340</v>
       </c>
       <c r="F432" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G432" t="s">
-        <v>1359</v>
+        <v>13</v>
       </c>
       <c r="H432" t="s">
         <v>13</v>
@@ -18767,22 +18782,22 @@
         <v>1250</v>
       </c>
       <c r="B433" t="s">
-        <v>1360</v>
+        <v>1341</v>
       </c>
       <c r="C433" t="s">
-        <v>1361</v>
+        <v>1342</v>
       </c>
       <c r="D433" t="s">
         <v>830</v>
       </c>
       <c r="E433" t="s">
-        <v>1362</v>
+        <v>1343</v>
       </c>
       <c r="F433" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G433" t="s">
-        <v>1359</v>
+        <v>1344</v>
       </c>
       <c r="H433" t="s">
         <v>13</v>
@@ -18799,22 +18814,22 @@
         <v>1250</v>
       </c>
       <c r="B434" t="s">
-        <v>1363</v>
+        <v>1345</v>
       </c>
       <c r="C434" t="s">
-        <v>1364</v>
+        <v>1346</v>
       </c>
       <c r="D434" t="s">
         <v>830</v>
       </c>
       <c r="E434" t="s">
-        <v>1365</v>
+        <v>1347</v>
       </c>
       <c r="F434" t="s">
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>1366</v>
+        <v>13</v>
       </c>
       <c r="H434" t="s">
         <v>13</v>
@@ -18831,22 +18846,22 @@
         <v>1250</v>
       </c>
       <c r="B435" t="s">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="C435" t="s">
-        <v>1368</v>
+        <v>1349</v>
       </c>
       <c r="D435" t="s">
         <v>830</v>
       </c>
       <c r="E435" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="F435" t="s">
         <v>13</v>
       </c>
       <c r="G435" t="s">
-        <v>13</v>
+        <v>1351</v>
       </c>
       <c r="H435" t="s">
         <v>13</v>
@@ -18863,22 +18878,22 @@
         <v>1250</v>
       </c>
       <c r="B436" t="s">
-        <v>1370</v>
+        <v>1352</v>
       </c>
       <c r="C436" t="s">
-        <v>1371</v>
+        <v>1353</v>
       </c>
       <c r="D436" t="s">
         <v>830</v>
       </c>
       <c r="E436" t="s">
-        <v>1372</v>
+        <v>1354</v>
       </c>
       <c r="F436" t="s">
         <v>13</v>
       </c>
       <c r="G436" t="s">
-        <v>13</v>
+        <v>1355</v>
       </c>
       <c r="H436" t="s">
         <v>13</v>
@@ -18895,22 +18910,22 @@
         <v>1250</v>
       </c>
       <c r="B437" t="s">
-        <v>1373</v>
+        <v>1356</v>
       </c>
       <c r="C437" t="s">
-        <v>1374</v>
+        <v>1357</v>
       </c>
       <c r="D437" t="s">
         <v>830</v>
       </c>
       <c r="E437" t="s">
-        <v>1375</v>
+        <v>1358</v>
       </c>
       <c r="F437" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G437" t="s">
-        <v>13</v>
+        <v>1359</v>
       </c>
       <c r="H437" t="s">
         <v>13</v>
@@ -18927,22 +18942,22 @@
         <v>1250</v>
       </c>
       <c r="B438" t="s">
-        <v>1376</v>
+        <v>1360</v>
       </c>
       <c r="C438" t="s">
-        <v>1377</v>
+        <v>1361</v>
       </c>
       <c r="D438" t="s">
-        <v>1243</v>
+        <v>830</v>
       </c>
       <c r="E438" t="s">
-        <v>1378</v>
+        <v>1362</v>
       </c>
       <c r="F438" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G438" t="s">
-        <v>13</v>
+        <v>1359</v>
       </c>
       <c r="H438" t="s">
         <v>13</v>
@@ -18959,22 +18974,22 @@
         <v>1250</v>
       </c>
       <c r="B439" t="s">
-        <v>1379</v>
+        <v>1363</v>
       </c>
       <c r="C439" t="s">
-        <v>1380</v>
+        <v>1364</v>
       </c>
       <c r="D439" t="s">
-        <v>1243</v>
+        <v>830</v>
       </c>
       <c r="E439" t="s">
-        <v>1381</v>
+        <v>1365</v>
       </c>
       <c r="F439" t="s">
         <v>13</v>
       </c>
       <c r="G439" t="s">
-        <v>13</v>
+        <v>1366</v>
       </c>
       <c r="H439" t="s">
         <v>13</v>
@@ -18991,16 +19006,16 @@
         <v>1250</v>
       </c>
       <c r="B440" t="s">
-        <v>1382</v>
+        <v>1367</v>
       </c>
       <c r="C440" t="s">
-        <v>1383</v>
+        <v>1368</v>
       </c>
       <c r="D440" t="s">
-        <v>1316</v>
+        <v>830</v>
       </c>
       <c r="E440" t="s">
-        <v>1384</v>
+        <v>1369</v>
       </c>
       <c r="F440" t="s">
         <v>13</v>
@@ -19023,16 +19038,16 @@
         <v>1250</v>
       </c>
       <c r="B441" t="s">
-        <v>1385</v>
+        <v>1370</v>
       </c>
       <c r="C441" t="s">
-        <v>1386</v>
+        <v>1371</v>
       </c>
       <c r="D441" t="s">
-        <v>1316</v>
+        <v>830</v>
       </c>
       <c r="E441" t="s">
-        <v>1387</v>
+        <v>1372</v>
       </c>
       <c r="F441" t="s">
         <v>13</v>
@@ -19055,16 +19070,16 @@
         <v>1250</v>
       </c>
       <c r="B442" t="s">
-        <v>1388</v>
+        <v>1373</v>
       </c>
       <c r="C442" t="s">
-        <v>1389</v>
+        <v>1374</v>
       </c>
       <c r="D442" t="s">
-        <v>1316</v>
+        <v>830</v>
       </c>
       <c r="E442" t="s">
-        <v>1390</v>
+        <v>1375</v>
       </c>
       <c r="F442" t="s">
         <v>13</v>
@@ -19087,16 +19102,16 @@
         <v>1250</v>
       </c>
       <c r="B443" t="s">
-        <v>1391</v>
+        <v>1376</v>
       </c>
       <c r="C443" t="s">
-        <v>1392</v>
+        <v>1377</v>
       </c>
       <c r="D443" t="s">
-        <v>1316</v>
+        <v>1243</v>
       </c>
       <c r="E443" t="s">
-        <v>1393</v>
+        <v>1378</v>
       </c>
       <c r="F443" t="s">
         <v>13</v>
@@ -19119,16 +19134,16 @@
         <v>1250</v>
       </c>
       <c r="B444" t="s">
-        <v>1394</v>
+        <v>1379</v>
       </c>
       <c r="C444" t="s">
-        <v>1395</v>
+        <v>1380</v>
       </c>
       <c r="D444" t="s">
-        <v>1316</v>
+        <v>1243</v>
       </c>
       <c r="E444" t="s">
-        <v>1396</v>
+        <v>1381</v>
       </c>
       <c r="F444" t="s">
         <v>13</v>
@@ -19151,22 +19166,22 @@
         <v>1250</v>
       </c>
       <c r="B445" t="s">
-        <v>1397</v>
+        <v>1382</v>
       </c>
       <c r="C445" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D445" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E445" t="s">
-        <v>1399</v>
+        <v>1384</v>
       </c>
       <c r="F445" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G445" t="s">
-        <v>1400</v>
+        <v>13</v>
       </c>
       <c r="H445" t="s">
         <v>13</v>
@@ -19183,16 +19198,16 @@
         <v>1250</v>
       </c>
       <c r="B446" t="s">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="C446" t="s">
-        <v>1402</v>
+        <v>1386</v>
       </c>
       <c r="D446" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E446" t="s">
-        <v>1403</v>
+        <v>1387</v>
       </c>
       <c r="F446" t="s">
         <v>13</v>
@@ -19215,22 +19230,22 @@
         <v>1250</v>
       </c>
       <c r="B447" t="s">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="C447" t="s">
-        <v>1405</v>
+        <v>1389</v>
       </c>
       <c r="D447" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E447" t="s">
-        <v>1406</v>
+        <v>1390</v>
       </c>
       <c r="F447" t="s">
         <v>13</v>
       </c>
       <c r="G447" t="s">
-        <v>1407</v>
+        <v>13</v>
       </c>
       <c r="H447" t="s">
         <v>13</v>
@@ -19247,22 +19262,22 @@
         <v>1250</v>
       </c>
       <c r="B448" t="s">
-        <v>1408</v>
+        <v>1391</v>
       </c>
       <c r="C448" t="s">
-        <v>1409</v>
+        <v>1392</v>
       </c>
       <c r="D448" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E448" t="s">
-        <v>1410</v>
+        <v>1393</v>
       </c>
       <c r="F448" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G448" t="s">
-        <v>1411</v>
+        <v>13</v>
       </c>
       <c r="H448" t="s">
         <v>13</v>
@@ -19279,16 +19294,16 @@
         <v>1250</v>
       </c>
       <c r="B449" t="s">
-        <v>1412</v>
+        <v>1394</v>
       </c>
       <c r="C449" t="s">
-        <v>1413</v>
+        <v>1395</v>
       </c>
       <c r="D449" t="s">
-        <v>830</v>
+        <v>1316</v>
       </c>
       <c r="E449" t="s">
-        <v>1414</v>
+        <v>1396</v>
       </c>
       <c r="F449" t="s">
         <v>13</v>
@@ -19311,22 +19326,22 @@
         <v>1250</v>
       </c>
       <c r="B450" t="s">
-        <v>1415</v>
+        <v>1397</v>
       </c>
       <c r="C450" t="s">
-        <v>1416</v>
+        <v>1398</v>
       </c>
       <c r="D450" t="s">
-        <v>895</v>
+        <v>830</v>
       </c>
       <c r="E450" t="s">
-        <v>1417</v>
+        <v>1399</v>
       </c>
       <c r="F450" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G450" t="s">
-        <v>13</v>
+        <v>1400</v>
       </c>
       <c r="H450" t="s">
         <v>13</v>
@@ -19343,16 +19358,16 @@
         <v>1250</v>
       </c>
       <c r="B451" t="s">
-        <v>1418</v>
+        <v>1401</v>
       </c>
       <c r="C451" t="s">
-        <v>1419</v>
+        <v>1402</v>
       </c>
       <c r="D451" t="s">
-        <v>895</v>
+        <v>830</v>
       </c>
       <c r="E451" t="s">
-        <v>1420</v>
+        <v>1403</v>
       </c>
       <c r="F451" t="s">
         <v>13</v>
@@ -19375,22 +19390,22 @@
         <v>1250</v>
       </c>
       <c r="B452" t="s">
-        <v>1421</v>
+        <v>1404</v>
       </c>
       <c r="C452" t="s">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="D452" t="s">
-        <v>1423</v>
+        <v>830</v>
       </c>
       <c r="E452" t="s">
-        <v>1424</v>
+        <v>1406</v>
       </c>
       <c r="F452" t="s">
         <v>13</v>
       </c>
       <c r="G452" t="s">
-        <v>13</v>
+        <v>1407</v>
       </c>
       <c r="H452" t="s">
         <v>13</v>
@@ -19407,22 +19422,22 @@
         <v>1250</v>
       </c>
       <c r="B453" t="s">
-        <v>1425</v>
+        <v>1408</v>
       </c>
       <c r="C453" t="s">
-        <v>1426</v>
+        <v>1409</v>
       </c>
       <c r="D453" t="s">
-        <v>1427</v>
+        <v>830</v>
       </c>
       <c r="E453" t="s">
-        <v>1428</v>
+        <v>1410</v>
       </c>
       <c r="F453" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G453" t="s">
-        <v>13</v>
+        <v>1411</v>
       </c>
       <c r="H453" t="s">
         <v>13</v>
@@ -19439,16 +19454,16 @@
         <v>1250</v>
       </c>
       <c r="B454" t="s">
-        <v>1429</v>
+        <v>1412</v>
       </c>
       <c r="C454" t="s">
-        <v>1430</v>
+        <v>1413</v>
       </c>
       <c r="D454" t="s">
-        <v>1124</v>
+        <v>830</v>
       </c>
       <c r="E454" t="s">
-        <v>1431</v>
+        <v>1414</v>
       </c>
       <c r="F454" t="s">
         <v>13</v>
@@ -19471,16 +19486,16 @@
         <v>1250</v>
       </c>
       <c r="B455" t="s">
-        <v>1432</v>
+        <v>1415</v>
       </c>
       <c r="C455" t="s">
-        <v>1433</v>
+        <v>1416</v>
       </c>
       <c r="D455" t="s">
-        <v>98</v>
+        <v>895</v>
       </c>
       <c r="E455" t="s">
-        <v>1434</v>
+        <v>1417</v>
       </c>
       <c r="F455" t="s">
         <v>13</v>
@@ -19503,16 +19518,16 @@
         <v>1250</v>
       </c>
       <c r="B456" t="s">
-        <v>1435</v>
+        <v>1418</v>
       </c>
       <c r="C456" t="s">
-        <v>1436</v>
+        <v>1419</v>
       </c>
       <c r="D456" t="s">
-        <v>1124</v>
+        <v>895</v>
       </c>
       <c r="E456" t="s">
-        <v>1437</v>
+        <v>1420</v>
       </c>
       <c r="F456" t="s">
         <v>13</v>
@@ -19535,16 +19550,16 @@
         <v>1250</v>
       </c>
       <c r="B457" t="s">
-        <v>1438</v>
+        <v>1421</v>
       </c>
       <c r="C457" t="s">
-        <v>1439</v>
+        <v>1422</v>
       </c>
       <c r="D457" t="s">
-        <v>1440</v>
+        <v>1423</v>
       </c>
       <c r="E457" t="s">
-        <v>13</v>
+        <v>1424</v>
       </c>
       <c r="F457" t="s">
         <v>13</v>
@@ -19567,16 +19582,16 @@
         <v>1250</v>
       </c>
       <c r="B458" t="s">
-        <v>1441</v>
+        <v>1425</v>
       </c>
       <c r="C458" t="s">
-        <v>1442</v>
+        <v>1426</v>
       </c>
       <c r="D458" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="E458" t="s">
-        <v>13</v>
+        <v>1428</v>
       </c>
       <c r="F458" t="s">
         <v>13</v>
@@ -19599,16 +19614,16 @@
         <v>1250</v>
       </c>
       <c r="B459" t="s">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="C459" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="D459" t="s">
-        <v>1445</v>
+        <v>1124</v>
       </c>
       <c r="E459" t="s">
-        <v>13</v>
+        <v>1431</v>
       </c>
       <c r="F459" t="s">
         <v>13</v>
@@ -19631,22 +19646,22 @@
         <v>1250</v>
       </c>
       <c r="B460" t="s">
-        <v>1446</v>
+        <v>1432</v>
       </c>
       <c r="C460" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
       <c r="D460" t="s">
-        <v>1448</v>
+        <v>98</v>
       </c>
       <c r="E460" t="s">
-        <v>1449</v>
+        <v>1434</v>
       </c>
       <c r="F460" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G460" t="s">
-        <v>1450</v>
+        <v>13</v>
       </c>
       <c r="H460" t="s">
         <v>13</v>
@@ -19663,22 +19678,22 @@
         <v>1250</v>
       </c>
       <c r="B461" t="s">
-        <v>1451</v>
+        <v>1435</v>
       </c>
       <c r="C461" t="s">
-        <v>1452</v>
+        <v>1436</v>
       </c>
       <c r="D461" t="s">
-        <v>1453</v>
+        <v>1124</v>
       </c>
       <c r="E461" t="s">
-        <v>1454</v>
+        <v>1437</v>
       </c>
       <c r="F461" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G461" t="s">
-        <v>1455</v>
+        <v>13</v>
       </c>
       <c r="H461" t="s">
         <v>13</v>
@@ -19695,22 +19710,22 @@
         <v>1250</v>
       </c>
       <c r="B462" t="s">
-        <v>1456</v>
+        <v>1438</v>
       </c>
       <c r="C462" t="s">
-        <v>1457</v>
+        <v>1439</v>
       </c>
       <c r="D462" t="s">
-        <v>830</v>
+        <v>1440</v>
       </c>
       <c r="E462" t="s">
-        <v>1458</v>
+        <v>13</v>
       </c>
       <c r="F462" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G462" t="s">
-        <v>1459</v>
+        <v>13</v>
       </c>
       <c r="H462" t="s">
         <v>13</v>
@@ -19727,22 +19742,22 @@
         <v>1250</v>
       </c>
       <c r="B463" t="s">
-        <v>1460</v>
+        <v>1441</v>
       </c>
       <c r="C463" t="s">
-        <v>1461</v>
+        <v>1442</v>
       </c>
       <c r="D463" t="s">
         <v>1423</v>
       </c>
       <c r="E463" t="s">
-        <v>1462</v>
+        <v>13</v>
       </c>
       <c r="F463" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G463" t="s">
-        <v>1463</v>
+        <v>13</v>
       </c>
       <c r="H463" t="s">
         <v>13</v>
@@ -19759,22 +19774,22 @@
         <v>1250</v>
       </c>
       <c r="B464" t="s">
-        <v>1464</v>
+        <v>1443</v>
       </c>
       <c r="C464" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="D464" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="E464" t="s">
-        <v>1466</v>
+        <v>13</v>
       </c>
       <c r="F464" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="G464" t="s">
-        <v>1467</v>
+        <v>13</v>
       </c>
       <c r="H464" t="s">
         <v>13</v>
@@ -19791,22 +19806,22 @@
         <v>1250</v>
       </c>
       <c r="B465" t="s">
-        <v>1468</v>
+        <v>1446</v>
       </c>
       <c r="C465" t="s">
-        <v>1469</v>
+        <v>1447</v>
       </c>
       <c r="D465" t="s">
-        <v>830</v>
+        <v>1448</v>
       </c>
       <c r="E465" t="s">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F465" t="s">
         <v>406</v>
       </c>
       <c r="G465" t="s">
-        <v>1471</v>
+        <v>1450</v>
       </c>
       <c r="H465" t="s">
         <v>13</v>
@@ -19823,22 +19838,22 @@
         <v>1250</v>
       </c>
       <c r="B466" t="s">
-        <v>1472</v>
+        <v>1451</v>
       </c>
       <c r="C466" t="s">
-        <v>1473</v>
+        <v>1452</v>
       </c>
       <c r="D466" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="E466" t="s">
-        <v>1474</v>
+        <v>1454</v>
       </c>
       <c r="F466" t="s">
         <v>406</v>
       </c>
       <c r="G466" t="s">
-        <v>1475</v>
+        <v>1455</v>
       </c>
       <c r="H466" t="s">
         <v>13</v>
@@ -19855,22 +19870,22 @@
         <v>1250</v>
       </c>
       <c r="B467" t="s">
-        <v>1476</v>
+        <v>1456</v>
       </c>
       <c r="C467" t="s">
-        <v>1477</v>
+        <v>1457</v>
       </c>
       <c r="D467" t="s">
-        <v>1478</v>
+        <v>830</v>
       </c>
       <c r="E467" t="s">
-        <v>1479</v>
+        <v>1458</v>
       </c>
       <c r="F467" t="s">
         <v>406</v>
       </c>
       <c r="G467" t="s">
-        <v>1480</v>
+        <v>1459</v>
       </c>
       <c r="H467" t="s">
         <v>13</v>
@@ -19887,22 +19902,22 @@
         <v>1250</v>
       </c>
       <c r="B468" t="s">
-        <v>1481</v>
+        <v>1460</v>
       </c>
       <c r="C468" t="s">
-        <v>1482</v>
+        <v>1461</v>
       </c>
       <c r="D468" t="s">
-        <v>1483</v>
+        <v>1423</v>
       </c>
       <c r="E468" t="s">
-        <v>1484</v>
+        <v>1462</v>
       </c>
       <c r="F468" t="s">
         <v>406</v>
       </c>
       <c r="G468" t="s">
-        <v>1485</v>
+        <v>1463</v>
       </c>
       <c r="H468" t="s">
         <v>13</v>
@@ -19919,22 +19934,22 @@
         <v>1250</v>
       </c>
       <c r="B469" t="s">
-        <v>1486</v>
+        <v>1464</v>
       </c>
       <c r="C469" t="s">
-        <v>1487</v>
+        <v>1465</v>
       </c>
       <c r="D469" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="E469" t="s">
-        <v>1488</v>
+        <v>1466</v>
       </c>
       <c r="F469" t="s">
         <v>406</v>
       </c>
       <c r="G469" t="s">
-        <v>1489</v>
+        <v>1467</v>
       </c>
       <c r="H469" t="s">
         <v>13</v>
@@ -19951,22 +19966,22 @@
         <v>1250</v>
       </c>
       <c r="B470" t="s">
-        <v>1490</v>
+        <v>1468</v>
       </c>
       <c r="C470" t="s">
-        <v>1491</v>
+        <v>1469</v>
       </c>
       <c r="D470" t="s">
-        <v>1478</v>
+        <v>830</v>
       </c>
       <c r="E470" t="s">
-        <v>1492</v>
+        <v>1470</v>
       </c>
       <c r="F470" t="s">
         <v>406</v>
       </c>
       <c r="G470" t="s">
-        <v>1493</v>
+        <v>1471</v>
       </c>
       <c r="H470" t="s">
         <v>13</v>
@@ -19980,25 +19995,25 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1494</v>
+        <v>1250</v>
       </c>
       <c r="B471" t="s">
-        <v>1495</v>
+        <v>1472</v>
       </c>
       <c r="C471" t="s">
-        <v>1496</v>
+        <v>1473</v>
       </c>
       <c r="D471" t="s">
-        <v>19</v>
+        <v>1423</v>
       </c>
       <c r="E471" t="s">
-        <v>13</v>
+        <v>1474</v>
       </c>
       <c r="F471" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G471" t="s">
-        <v>13</v>
+        <v>1475</v>
       </c>
       <c r="H471" t="s">
         <v>13</v>
@@ -20012,25 +20027,25 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>1494</v>
+        <v>1250</v>
       </c>
       <c r="B472" t="s">
-        <v>1497</v>
+        <v>1476</v>
       </c>
       <c r="C472" t="s">
-        <v>1498</v>
+        <v>1477</v>
       </c>
       <c r="D472" t="s">
-        <v>1499</v>
+        <v>1478</v>
       </c>
       <c r="E472" t="s">
-        <v>13</v>
+        <v>1479</v>
       </c>
       <c r="F472" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G472" t="s">
-        <v>13</v>
+        <v>1480</v>
       </c>
       <c r="H472" t="s">
         <v>13</v>
@@ -20044,25 +20059,25 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1494</v>
+        <v>1250</v>
       </c>
       <c r="B473" t="s">
-        <v>1500</v>
+        <v>1481</v>
       </c>
       <c r="C473" t="s">
-        <v>1501</v>
+        <v>1482</v>
       </c>
       <c r="D473" t="s">
-        <v>1502</v>
+        <v>1483</v>
       </c>
       <c r="E473" t="s">
-        <v>13</v>
+        <v>1484</v>
       </c>
       <c r="F473" t="s">
-        <v>13</v>
+        <v>406</v>
       </c>
       <c r="G473" t="s">
-        <v>13</v>
+        <v>1485</v>
       </c>
       <c r="H473" t="s">
         <v>13</v>
@@ -20076,40 +20091,200 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D474" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E474" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F474" t="s">
+        <v>406</v>
+      </c>
+      <c r="G474" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H474" t="s">
+        <v>13</v>
+      </c>
+      <c r="I474" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J474" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C475" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D475" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E475" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F475" t="s">
+        <v>406</v>
+      </c>
+      <c r="G475" t="s">
+        <v>1493</v>
+      </c>
+      <c r="H475" t="s">
+        <v>13</v>
+      </c>
+      <c r="I475" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J475" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
         <v>1494</v>
       </c>
-      <c r="B474" t="s">
+      <c r="B476" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D476" t="s">
+        <v>19</v>
+      </c>
+      <c r="E476" t="s">
+        <v>13</v>
+      </c>
+      <c r="F476" t="s">
+        <v>13</v>
+      </c>
+      <c r="G476" t="s">
+        <v>13</v>
+      </c>
+      <c r="H476" t="s">
+        <v>13</v>
+      </c>
+      <c r="I476" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J476" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D477" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E477" t="s">
+        <v>13</v>
+      </c>
+      <c r="F477" t="s">
+        <v>13</v>
+      </c>
+      <c r="G477" t="s">
+        <v>13</v>
+      </c>
+      <c r="H477" t="s">
+        <v>13</v>
+      </c>
+      <c r="I477" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J477" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D478" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E478" t="s">
+        <v>13</v>
+      </c>
+      <c r="F478" t="s">
+        <v>13</v>
+      </c>
+      <c r="G478" t="s">
+        <v>13</v>
+      </c>
+      <c r="H478" t="s">
+        <v>13</v>
+      </c>
+      <c r="I478" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J478" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B479" t="s">
         <v>1503</v>
       </c>
-      <c r="C474" t="s">
+      <c r="C479" t="s">
         <v>1504</v>
       </c>
-      <c r="D474" t="s">
+      <c r="D479" t="s">
         <v>1505</v>
       </c>
-      <c r="E474" t="s">
-        <v>13</v>
-      </c>
-      <c r="F474" t="s">
-        <v>13</v>
-      </c>
-      <c r="G474" t="s">
-        <v>13</v>
-      </c>
-      <c r="H474" t="s">
-        <v>13</v>
-      </c>
-      <c r="I474" t="s">
-        <v>1512</v>
-      </c>
-      <c r="J474" t="s">
+      <c r="E479" t="s">
+        <v>13</v>
+      </c>
+      <c r="F479" t="s">
+        <v>13</v>
+      </c>
+      <c r="G479" t="s">
+        <v>13</v>
+      </c>
+      <c r="H479" t="s">
+        <v>13</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J479" t="s">
         <v>1512</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A308:H474 A4:H281 A284:H303 A1:H2" numberStoredAsText="1"/>
+    <ignoredError sqref="A385:H479 A4:H281 A284:H303 A1:H2 A380:H383 A375:H378 A370:H373 A365:H368 A308:H363" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>